--- a/04_Figures/F04_association/modules/training/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/training/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -492,16 +486,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000530345937546384</v>
+        <v>0.00241133373013234</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0815696799909676</v>
+        <v>0.411166901919318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.935588049615408</v>
+        <v>0.681681906936696</v>
       </c>
       <c r="G2" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +509,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00449068136710185</v>
+        <v>-0.00132185742354327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.795676785196919</v>
+        <v>-0.225497378598267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.433130709966406</v>
+        <v>0.821975109470873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +532,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00308785474993345</v>
+        <v>0.004148315488715</v>
       </c>
       <c r="E4" t="n">
-        <v>0.490094066176764</v>
+        <v>0.679292936558337</v>
       </c>
       <c r="F4" t="n">
-        <v>0.628009575647202</v>
+        <v>0.498257561642619</v>
       </c>
       <c r="G4" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000567839859682525</v>
+        <v>-0.0029742453145744</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.112846393822137</v>
+        <v>-0.489196460120684</v>
       </c>
       <c r="F5" t="n">
-        <v>0.910983663320286</v>
+        <v>0.625593627326935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00552254262937288</v>
+        <v>0.00605403244143015</v>
       </c>
       <c r="E6" t="n">
-        <v>1.03534042067736</v>
+        <v>1.03143130272715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.309655865495623</v>
+        <v>0.304408397543962</v>
       </c>
       <c r="G6" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +601,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00567032249052361</v>
+        <v>-0.000517785557181888</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.781142282961856</v>
+        <v>-0.0845702296456205</v>
       </c>
       <c r="F7" t="n">
-        <v>0.441485997172007</v>
+        <v>0.932743686467848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +624,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00431627900654132</v>
+        <v>0.00053414624792846</v>
       </c>
       <c r="E8" t="n">
-        <v>0.775318046075538</v>
+        <v>0.0909945404067549</v>
       </c>
       <c r="F8" t="n">
-        <v>0.444861298003023</v>
+        <v>0.927648314023023</v>
       </c>
       <c r="G8" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +647,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000550387414048827</v>
+        <v>0.00320262110574785</v>
       </c>
       <c r="E9" t="n">
-        <v>0.103670527124297</v>
+        <v>0.531727019786199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.918193809976528</v>
+        <v>0.595895904901098</v>
       </c>
       <c r="G9" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +670,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00248318340548715</v>
+        <v>0.000479205289615867</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.396932125453581</v>
+        <v>0.0791829311508542</v>
       </c>
       <c r="F10" t="n">
-        <v>0.69452457949597</v>
+        <v>0.937018724919918</v>
       </c>
       <c r="G10" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00146604434339889</v>
+        <v>-0.00265155289482068</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.197049897086299</v>
+        <v>-0.430068956085416</v>
       </c>
       <c r="F11" t="n">
-        <v>0.845258111401243</v>
+        <v>0.667915125812564</v>
       </c>
       <c r="G11" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
     <row r="12">
@@ -722,62 +716,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.00725912706920651</v>
+        <v>0.00196497559215979</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.36541039839994</v>
+        <v>0.323081286504438</v>
       </c>
       <c r="F12" t="n">
-        <v>0.183345601751905</v>
+        <v>0.747194747077722</v>
       </c>
       <c r="G12" t="n">
-        <v>0.935588049615408</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00245985356963536</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.370342668013783</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.714004489956319</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.935588049615408</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00105692326428923</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.174678531382195</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.862630002802839</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.935588049615408</v>
+        <v>0.937018724919918</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +764,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -825,21 +773,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000108539109210631</v>
+        <v>0.0000143230281940479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.285759188229677</v>
+        <v>0.427298590928897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.777398404056334</v>
+        <v>0.670364440423439</v>
       </c>
       <c r="G2" t="n">
-        <v>0.94514305116327</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -848,21 +796,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000335898831767306</v>
+        <v>-0.0000337986493519825</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0397770070323</v>
+        <v>-1.01547613911335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.308317548545153</v>
+        <v>0.313085888122625</v>
       </c>
       <c r="G3" t="n">
-        <v>0.819223995881155</v>
+        <v>0.92732151075383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -871,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000422294043367586</v>
+        <v>0.0000356866698469231</v>
       </c>
       <c r="E4" t="n">
-        <v>1.17404845823568</v>
+        <v>1.00059237179297</v>
       </c>
       <c r="F4" t="n">
-        <v>0.251352151842217</v>
+        <v>0.32018436721404</v>
       </c>
       <c r="G4" t="n">
-        <v>0.819223995881155</v>
+        <v>0.92732151075383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -894,21 +842,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000251153300343523</v>
+        <v>0.00000661858026710717</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.891234018599658</v>
+        <v>0.185975090546448</v>
       </c>
       <c r="F5" t="n">
-        <v>0.381234513858704</v>
+        <v>0.852957477528701</v>
       </c>
       <c r="G5" t="n">
-        <v>0.826008113360524</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -917,21 +865,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000313830013363735</v>
+        <v>0.0000349058760058986</v>
       </c>
       <c r="E6" t="n">
-        <v>1.02503523879242</v>
+        <v>1.03959866607264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.315086152261983</v>
+        <v>0.301807184514518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.819223995881155</v>
+        <v>0.92732151075383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -940,21 +888,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000244469620012894</v>
+        <v>0.00000991538002876113</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.567859490671067</v>
+        <v>0.2760433170475</v>
       </c>
       <c r="F7" t="n">
-        <v>0.575155541859525</v>
+        <v>0.78326054990343</v>
       </c>
       <c r="G7" t="n">
-        <v>0.873776188633835</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -963,21 +911,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000169200666031089</v>
+        <v>-0.00000296259527535903</v>
       </c>
       <c r="E8" t="n">
-        <v>0.523905478339074</v>
+        <v>-0.0882430952105977</v>
       </c>
       <c r="F8" t="n">
-        <v>0.604921976746501</v>
+        <v>0.929914495842446</v>
       </c>
       <c r="G8" t="n">
-        <v>0.873776188633835</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -986,21 +934,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00000085190730402801</v>
+        <v>0.00000378752193891995</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0280062777248854</v>
+        <v>0.107982887719545</v>
       </c>
       <c r="F9" t="n">
-        <v>0.977877762078996</v>
+        <v>0.91429251361036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.977877762078996</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1009,21 +957,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00000646613724966954</v>
+        <v>0.00000360917934535153</v>
       </c>
       <c r="E10" t="n">
-        <v>0.176804848852705</v>
+        <v>0.102302431945746</v>
       </c>
       <c r="F10" t="n">
-        <v>0.861075013681695</v>
+        <v>0.918784815567636</v>
       </c>
       <c r="G10" t="n">
-        <v>0.94514305116327</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1032,21 +980,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0000558798238359975</v>
+        <v>-0.0000235486897597807</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.31317891546692</v>
+        <v>-0.649172860352774</v>
       </c>
       <c r="F11" t="n">
-        <v>0.200955137415971</v>
+        <v>0.518174608451968</v>
       </c>
       <c r="G11" t="n">
-        <v>0.819223995881155</v>
+        <v>0.929914495842446</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1055,62 +1003,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000055388598549418</v>
+        <v>0.0000341586778588879</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.86916260890687</v>
+        <v>0.965770794221541</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0732653175390369</v>
+        <v>0.337207822092302</v>
       </c>
       <c r="G12" t="n">
-        <v>0.819223995881155</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0000221918399650368</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.572214887047939</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5722463743692</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.873776188633835</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.00000570569401357682</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.162202826334556</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.872439739535326</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.94514305116327</v>
+        <v>0.92732151075383</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1051,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1158,21 +1060,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000000413406648666906</v>
+        <v>0.0000147217117411815</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0101137971659875</v>
+        <v>0.420961883287643</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99201330009221</v>
+        <v>0.675530540649696</v>
       </c>
       <c r="G2" t="n">
-        <v>0.99201330009221</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1181,21 +1083,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000337554640217503</v>
+        <v>-0.0000445038140198066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.977432627094939</v>
+        <v>-1.2940047439822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.338012735696034</v>
+        <v>0.201423649211838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.732360927341408</v>
+        <v>0.937130962683301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1204,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000524659625265119</v>
+        <v>0.0000349191426565369</v>
       </c>
       <c r="E4" t="n">
-        <v>1.37415616295503</v>
+        <v>0.907345776708127</v>
       </c>
       <c r="F4" t="n">
-        <v>0.181970778828003</v>
+        <v>0.368440495064197</v>
       </c>
       <c r="G4" t="n">
-        <v>0.606341089686216</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1227,21 +1129,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000035920729461759</v>
+        <v>0.0000166555417076123</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.22268372944163</v>
+        <v>0.435530172205759</v>
       </c>
       <c r="F5" t="n">
-        <v>0.233208111417776</v>
+        <v>0.664993491327523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.606341089686216</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1250,21 +1152,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000413461238325256</v>
+        <v>0.0000449665594817045</v>
       </c>
       <c r="E6" t="n">
-        <v>1.28536442732647</v>
+        <v>1.28888493022949</v>
       </c>
       <c r="F6" t="n">
-        <v>0.210814225110358</v>
+        <v>0.203184608457303</v>
       </c>
       <c r="G6" t="n">
-        <v>0.606341089686216</v>
+        <v>0.937130962683301</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1273,21 +1175,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000283861026907639</v>
+        <v>-0.000000917588164830249</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.611665122079229</v>
+        <v>-0.0236175259026505</v>
       </c>
       <c r="F7" t="n">
-        <v>0.546455674159057</v>
+        <v>0.981248757189556</v>
       </c>
       <c r="G7" t="n">
-        <v>0.810162247797704</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1296,21 +1198,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000181592062310918</v>
+        <v>0.00000324755199756231</v>
       </c>
       <c r="E8" t="n">
-        <v>0.52746271214355</v>
+        <v>0.0926471286690208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.60266875548289</v>
+        <v>0.926542550248741</v>
       </c>
       <c r="G8" t="n">
-        <v>0.810162247797704</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1319,21 +1221,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00000815556342306966</v>
+        <v>-0.0000036689897190565</v>
       </c>
       <c r="E9" t="n">
-        <v>0.252761649371747</v>
+        <v>-0.0978854805418462</v>
       </c>
       <c r="F9" t="n">
-        <v>0.802584227162933</v>
+        <v>0.92240234168716</v>
       </c>
       <c r="G9" t="n">
-        <v>0.869466246093177</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1342,21 +1244,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000160325748099062</v>
+        <v>-0.00000167459666478418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.409842774608987</v>
+        <v>-0.0442886683506058</v>
       </c>
       <c r="F10" t="n">
-        <v>0.685521901982673</v>
+        <v>0.964845192243268</v>
       </c>
       <c r="G10" t="n">
-        <v>0.810162247797704</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1365,21 +1267,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0000690010672317532</v>
+        <v>-0.0000217634550216641</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.52042092736333</v>
+        <v>-0.552019641196775</v>
       </c>
       <c r="F11" t="n">
-        <v>0.141347224915859</v>
+        <v>0.58331715129557</v>
       </c>
       <c r="G11" t="n">
-        <v>0.606341089686216</v>
+        <v>0.981248757189556</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1388,62 +1290,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0000560984109647732</v>
+        <v>0.0000434714312281015</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.77090875756487</v>
+        <v>1.14966401914103</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0891554337582321</v>
+        <v>0.2555811716409</v>
       </c>
       <c r="G12" t="n">
-        <v>0.606341089686216</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0000202530767182689</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.484769465886404</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.632193168716597</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.810162247797704</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000154241006574534</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.410711163272161</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.684893487207859</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.810162247797704</v>
+        <v>0.937130962683301</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1491,21 +1347,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00666887933473895</v>
+        <v>0.00778999465776515</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2153259260157</v>
+        <v>0.298457322989752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.831292949793279</v>
+        <v>0.766681817959241</v>
       </c>
       <c r="G2" t="n">
-        <v>0.971334668190171</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1514,21 +1370,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0013990033915867</v>
+        <v>0.0427885733575753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0523341743262352</v>
+        <v>1.69217406440318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.958686154013925</v>
+        <v>0.0972942537434069</v>
       </c>
       <c r="G3" t="n">
-        <v>0.971334668190171</v>
+        <v>0.472021993506016</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1537,21 +1393,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0409850633726925</v>
+        <v>-0.00344611543286836</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.41772586278465</v>
+        <v>-0.117493982637278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.168845381829618</v>
+        <v>0.906973896387141</v>
       </c>
       <c r="G4" t="n">
-        <v>0.507656435184352</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1560,21 +1416,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0361383568814269</v>
+        <v>-0.0397706053965333</v>
       </c>
       <c r="E5" t="n">
-        <v>1.65513446111858</v>
+        <v>-1.40356767033695</v>
       </c>
       <c r="F5" t="n">
-        <v>0.110633272485615</v>
+        <v>0.167080835720459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.507656435184352</v>
+        <v>0.472021993506016</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1583,21 +1439,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00479380887699255</v>
+        <v>-0.00381319763011214</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.189945695548512</v>
+        <v>-0.144030083158321</v>
       </c>
       <c r="F6" t="n">
-        <v>0.850914285911924</v>
+        <v>0.886098189033269</v>
       </c>
       <c r="G6" t="n">
-        <v>0.971334668190171</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1606,21 +1462,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00128649620769414</v>
+        <v>-0.00522279224071747</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0363027658043961</v>
+        <v>-0.177786617729245</v>
       </c>
       <c r="F7" t="n">
-        <v>0.971334668190171</v>
+        <v>0.859661636103323</v>
       </c>
       <c r="G7" t="n">
-        <v>0.971334668190171</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1629,21 +1485,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0327685529891551</v>
+        <v>0.0150031270594946</v>
       </c>
       <c r="E8" t="n">
-        <v>1.28766276735625</v>
+        <v>0.575845737397152</v>
       </c>
       <c r="F8" t="n">
-        <v>0.209875973392192</v>
+        <v>0.567491935172789</v>
       </c>
       <c r="G8" t="n">
-        <v>0.507656435184352</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1652,21 +1508,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00781263169852311</v>
+        <v>0.0424300356323616</v>
       </c>
       <c r="E9" t="n">
-        <v>0.318869641895924</v>
+        <v>1.54109033380484</v>
       </c>
       <c r="F9" t="n">
-        <v>0.752523908347112</v>
+        <v>0.130063011487129</v>
       </c>
       <c r="G9" t="n">
-        <v>0.971334668190171</v>
+        <v>0.472021993506016</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1675,21 +1531,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0352585351944463</v>
+        <v>0.0175917960969393</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.21935078139024</v>
+        <v>0.61972998581742</v>
       </c>
       <c r="F10" t="n">
-        <v>0.234302970085085</v>
+        <v>0.538456109084058</v>
       </c>
       <c r="G10" t="n">
-        <v>0.507656435184352</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1698,21 +1554,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0719043223027584</v>
+        <v>-0.00995437470733506</v>
       </c>
       <c r="E11" t="n">
-        <v>2.18321979600399</v>
+        <v>-0.332534660198181</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0388053531312165</v>
+        <v>0.740977834516912</v>
       </c>
       <c r="G11" t="n">
-        <v>0.504469590705814</v>
+        <v>0.906973896387141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1721,62 +1577,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0131266784915903</v>
+        <v>-0.039334106664319</v>
       </c>
       <c r="E12" t="n">
-        <v>0.51609761126855</v>
+        <v>-1.38832285647435</v>
       </c>
       <c r="F12" t="n">
-        <v>0.610405974885795</v>
+        <v>0.171644361274915</v>
       </c>
       <c r="G12" t="n">
-        <v>0.971334668190171</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0101588756770103</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.319793790962138</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.751831661817348</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.971334668190171</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0365218237417413</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.32178676116166</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.198430473247216</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.507656435184352</v>
+        <v>0.472021993506016</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1824,21 +1634,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000500534000743265</v>
+        <v>-0.000553504398295241</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.291248783891319</v>
+        <v>-0.349187755009002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.772656461806621</v>
+        <v>0.727504771874406</v>
       </c>
       <c r="G2" t="n">
-        <v>0.772656461806621</v>
+        <v>0.857995960255689</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1847,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00100455601498451</v>
+        <v>-0.000780765751582357</v>
       </c>
       <c r="E3" t="n">
-        <v>0.653393417416082</v>
+        <v>-0.492559482494909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.517961628251023</v>
+        <v>0.623142176651721</v>
       </c>
       <c r="G3" t="n">
-        <v>0.772656461806621</v>
+        <v>0.857995960255689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1870,21 +1680,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00162949900608577</v>
+        <v>0.00176587430943074</v>
       </c>
       <c r="E4" t="n">
-        <v>0.98246446642526</v>
+        <v>1.1140321335067</v>
       </c>
       <c r="F4" t="n">
-        <v>0.33291232654775</v>
+        <v>0.267289776752953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.772656461806621</v>
+        <v>0.847588445407278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1893,21 +1703,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000486190655726642</v>
+        <v>0.00295394559850471</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.347147871627538</v>
+        <v>1.86354730899607</v>
       </c>
       <c r="F5" t="n">
-        <v>0.730651271491794</v>
+        <v>0.0646072243119973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.772656461806621</v>
+        <v>0.71067946743197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1916,21 +1726,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000525596960013725</v>
+        <v>-0.000265256770188119</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.353652192785</v>
+        <v>-0.16734178873412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.725815178988629</v>
+        <v>0.867357219828527</v>
       </c>
       <c r="G6" t="n">
-        <v>0.772656461806621</v>
+        <v>0.867357219828527</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1939,21 +1749,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000770625348506155</v>
+        <v>-0.000490444771522587</v>
       </c>
       <c r="E7" t="n">
-        <v>0.404908321161458</v>
+        <v>-0.309405506534974</v>
       </c>
       <c r="F7" t="n">
-        <v>0.688118416593241</v>
+        <v>0.757500951802131</v>
       </c>
       <c r="G7" t="n">
-        <v>0.772656461806621</v>
+        <v>0.857995960255689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1962,21 +1772,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00113060632698723</v>
+        <v>0.000584965768709997</v>
       </c>
       <c r="E8" t="n">
-        <v>0.745173944014228</v>
+        <v>0.369035700822028</v>
       </c>
       <c r="F8" t="n">
-        <v>0.461361945365059</v>
+        <v>0.712692389067842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.772656461806621</v>
+        <v>0.857995960255689</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1985,21 +1795,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000509459460616845</v>
+        <v>0.000443666813217488</v>
       </c>
       <c r="E9" t="n">
-        <v>0.349200322488921</v>
+        <v>0.279894828219191</v>
       </c>
       <c r="F9" t="n">
-        <v>0.729124013243906</v>
+        <v>0.779996327505172</v>
       </c>
       <c r="G9" t="n">
-        <v>0.772656461806621</v>
+        <v>0.857995960255689</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2008,21 +1818,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0029447227639493</v>
+        <v>0.00126462163342912</v>
       </c>
       <c r="E10" t="n">
-        <v>1.85085983849944</v>
+        <v>0.797808274826726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0730221588330683</v>
+        <v>0.42641464965244</v>
       </c>
       <c r="G10" t="n">
-        <v>0.772656461806621</v>
+        <v>0.857995960255689</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2031,21 +1841,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00293167753911166</v>
+        <v>-0.00208785928354037</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.57281740145426</v>
+        <v>-1.31716188387953</v>
       </c>
       <c r="F11" t="n">
-        <v>0.125157446613382</v>
+        <v>0.190066279770927</v>
       </c>
       <c r="G11" t="n">
-        <v>0.772656461806621</v>
+        <v>0.847588445407278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2054,62 +1864,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.00110787188050534</v>
+        <v>0.00162145980770125</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.743998200044557</v>
+        <v>1.02292576505692</v>
       </c>
       <c r="F12" t="n">
-        <v>0.462063475401331</v>
+        <v>0.308213980148101</v>
       </c>
       <c r="G12" t="n">
-        <v>0.772656461806621</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00207009339756372</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.20452759232455</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.236825266796033</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.772656461806621</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.000604770260465658</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.373602442474413</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.711053653816858</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.772656461806621</v>
+        <v>0.847588445407278</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +1912,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -2157,21 +1921,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0090002481555386</v>
+        <v>-0.00781894060910984</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.924062235381531</v>
+        <v>-0.891076983257613</v>
       </c>
       <c r="F2" t="n">
-        <v>0.361757551232839</v>
+        <v>0.374656316936546</v>
       </c>
       <c r="G2" t="n">
-        <v>0.702522023756914</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -2180,21 +1944,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00889791055243767</v>
+        <v>0.00556518665382323</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.07259421808599</v>
+        <v>0.634230387806834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.290765912195787</v>
+        <v>0.527127719412673</v>
       </c>
       <c r="G3" t="n">
-        <v>0.702522023756914</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -2203,21 +1967,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00680429725284685</v>
+        <v>-0.0113236772498961</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.709914120163221</v>
+        <v>-1.29049044719231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.482443109182264</v>
+        <v>0.199340947747539</v>
       </c>
       <c r="G4" t="n">
-        <v>0.702522023756914</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -2226,21 +1990,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00574380156060658</v>
+        <v>-0.0022530192032237</v>
       </c>
       <c r="E5" t="n">
-        <v>0.712632578999281</v>
+        <v>-0.256762860238506</v>
       </c>
       <c r="F5" t="n">
-        <v>0.480779717008827</v>
+        <v>0.797797918688059</v>
       </c>
       <c r="G5" t="n">
-        <v>0.702522023756914</v>
+        <v>0.853647336465222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -2249,21 +2013,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00600174559024763</v>
+        <v>0.0062365768162108</v>
       </c>
       <c r="E6" t="n">
-        <v>0.70353142011065</v>
+        <v>0.710744630643277</v>
       </c>
       <c r="F6" t="n">
-        <v>0.486361401062479</v>
+        <v>0.47861024277036</v>
       </c>
       <c r="G6" t="n">
-        <v>0.702522023756914</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -2272,21 +2036,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0256612773973272</v>
+        <v>-0.0091712754699133</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.63265464333917</v>
+        <v>-1.04519434114045</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0125065852954548</v>
+        <v>0.298016690286665</v>
       </c>
       <c r="G7" t="n">
-        <v>0.162585608840912</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -2295,21 +2059,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00453662897785576</v>
+        <v>0.00162210377360065</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.530860650781726</v>
+        <v>0.184861275890342</v>
       </c>
       <c r="F8" t="n">
-        <v>0.598855517876234</v>
+        <v>0.853647336465222</v>
       </c>
       <c r="G8" t="n">
-        <v>0.778512173239105</v>
+        <v>0.853647336465222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -2318,21 +2082,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00138658873067195</v>
+        <v>-0.00476119001335993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.165408006615033</v>
+        <v>-0.542603793265549</v>
       </c>
       <c r="F9" t="n">
-        <v>0.869571009207976</v>
+        <v>0.588400644272883</v>
       </c>
       <c r="G9" t="n">
-        <v>0.88764875876255</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -2341,21 +2105,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00135287270076517</v>
+        <v>-0.0144842501650481</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.142309232683817</v>
+        <v>-1.6506816699416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.88764875876255</v>
+        <v>0.101396895661087</v>
       </c>
       <c r="G10" t="n">
-        <v>0.88764875876255</v>
+        <v>0.557682926135981</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2364,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0113286483882132</v>
+        <v>0.01685250197659</v>
       </c>
       <c r="E11" t="n">
-        <v>1.04156386119776</v>
+        <v>1.92057688789024</v>
       </c>
       <c r="F11" t="n">
-        <v>0.304728820067572</v>
+        <v>0.0571381637136113</v>
       </c>
       <c r="G11" t="n">
-        <v>0.702522023756914</v>
+        <v>0.557682926135981</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2387,62 +2151,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00270112626849363</v>
+        <v>-0.00614954819730692</v>
       </c>
       <c r="E12" t="n">
-        <v>0.315205848245954</v>
+        <v>-0.700826509625757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.754470063112752</v>
+        <v>0.484756814512973</v>
       </c>
       <c r="G12" t="n">
-        <v>0.88764875876255</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0167006227164348</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.83192938559948</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0754509103409578</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.490430917216226</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.010444024879532</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.2029447027273</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.237042054521387</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.702522023756914</v>
+        <v>0.71915634300019</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2199,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2490,21 +2208,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0430747700232114</v>
+        <v>0.111789367422087</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.385504144360803</v>
+        <v>1.11582145618419</v>
       </c>
       <c r="F2" t="n">
-        <v>0.702794780177418</v>
+        <v>0.266525753627693</v>
       </c>
       <c r="G2" t="n">
-        <v>0.940396520325286</v>
+        <v>0.602300836511116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2513,21 +2231,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.136687571402986</v>
+        <v>-0.0100920897247498</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4370360155226</v>
+        <v>-0.10044366313777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.161855705294225</v>
+        <v>0.920144504876006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.778717144016546</v>
+        <v>0.989564095417616</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2536,21 +2254,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0258043513804933</v>
+        <v>0.138133401409057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.236805766368346</v>
+        <v>1.34017954620811</v>
       </c>
       <c r="F4" t="n">
-        <v>0.814541817815922</v>
+        <v>0.182489270892456</v>
       </c>
       <c r="G4" t="n">
-        <v>0.940396520325286</v>
+        <v>0.602300836511116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2559,21 +2277,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0146037994838802</v>
+        <v>-0.121538346334148</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.167666152642294</v>
+        <v>-1.18241178560179</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86805832645411</v>
+        <v>0.239167856108671</v>
       </c>
       <c r="G5" t="n">
-        <v>0.940396520325286</v>
+        <v>0.602300836511116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2582,21 +2300,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.071586959091947</v>
+        <v>0.078258532800438</v>
       </c>
       <c r="E6" t="n">
-        <v>0.769650823649027</v>
+        <v>0.777181845344092</v>
       </c>
       <c r="F6" t="n">
-        <v>0.447990527677336</v>
+        <v>0.438442077954699</v>
       </c>
       <c r="G6" t="n">
-        <v>0.831982408543624</v>
+        <v>0.688980408214526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2605,21 +2323,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0361729802462519</v>
+        <v>-0.0411266369279065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.286905938487288</v>
+        <v>-0.396941151171125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.77630954185644</v>
+        <v>0.692051906112495</v>
       </c>
       <c r="G7" t="n">
-        <v>0.940396520325286</v>
+        <v>0.951571370904681</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2628,21 +2346,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.115759056624489</v>
+        <v>0.0141831166638813</v>
       </c>
       <c r="E8" t="n">
-        <v>1.22231356465693</v>
+        <v>0.141043327887816</v>
       </c>
       <c r="F8" t="n">
-        <v>0.231840215058017</v>
+        <v>0.888050730654935</v>
       </c>
       <c r="G8" t="n">
-        <v>0.778717144016546</v>
+        <v>0.989564095417616</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2651,21 +2369,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00232896269703435</v>
+        <v>0.11227488210206</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0253633864731342</v>
+        <v>1.09898939946495</v>
       </c>
       <c r="F9" t="n">
-        <v>0.979946102411901</v>
+        <v>0.273773107505053</v>
       </c>
       <c r="G9" t="n">
-        <v>0.979946102411901</v>
+        <v>0.602300836511116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2674,21 +2392,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.113237883004263</v>
+        <v>0.0930190516412853</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.06822457226624</v>
+        <v>0.907121587817737</v>
       </c>
       <c r="F10" t="n">
-        <v>0.294597521889212</v>
+        <v>0.365995513199062</v>
       </c>
       <c r="G10" t="n">
-        <v>0.778717144016546</v>
+        <v>0.67099177419828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2697,21 +2415,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0298229973617566</v>
+        <v>-0.119815231926908</v>
       </c>
       <c r="E11" t="n">
-        <v>0.233124500543071</v>
+        <v>-1.15381949423971</v>
       </c>
       <c r="F11" t="n">
-        <v>0.81737079784865</v>
+        <v>0.250659013866129</v>
       </c>
       <c r="G11" t="n">
-        <v>0.940396520325286</v>
+        <v>0.602300836511116</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2720,62 +2438,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0871557780340243</v>
+        <v>0.00135222768200906</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.931889113182232</v>
+        <v>0.0131046396132396</v>
       </c>
       <c r="F12" t="n">
-        <v>0.359407912623021</v>
+        <v>0.989564095417616</v>
       </c>
       <c r="G12" t="n">
-        <v>0.778717144016546</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.117012427838741</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.03989723920503</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.307337803066406</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.778717144016546</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0981309087498251</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.95499504385628</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.347802137088055</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.778717144016546</v>
+        <v>0.989564095417616</v>
       </c>
     </row>
   </sheetData>
@@ -2791,45 +2463,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2838,50 +2510,50 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00248318340548715</v>
+        <v>0.00241133373013234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00680429725284685</v>
+        <v>0.0062365768162108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2890,24 +2562,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00100455601498451</v>
+        <v>0.000780765751582357</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2916,24 +2588,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000244469620012894</v>
+        <v>0.0000143230281940479</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2942,50 +2614,50 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000283861026907639</v>
+        <v>0.0000166555417076123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0131266784915903</v>
+        <v>0.0150031270594946</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2994,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.071586959091947</v>
+        <v>0.0930190516412853</v>
       </c>
     </row>
   </sheetData>
